--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,760 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121573227</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103629</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>711891</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6375090</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121573220</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101257</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>711778</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6374934</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121573221</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103629</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>711803</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6374919</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121573222</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106483</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1897</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Korskovall</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Melampyrum cristatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>711803</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6374919</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spridd 25 m mot NV.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121573224</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103025</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>711813</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6374960</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121573226</v>
+      </c>
+      <c r="B8" t="n">
+        <v>108727</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>711891</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6375090</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121573223</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101257</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>711808</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6374924</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121573227</v>
+        <v>121573224</v>
       </c>
       <c r="B3" t="n">
-        <v>103629</v>
+        <v>103026</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220164</v>
+        <v>222002</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711891</v>
+        <v>711813</v>
       </c>
       <c r="R3" t="n">
-        <v>6375090</v>
+        <v>6374960</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121573220</v>
+        <v>121573222</v>
       </c>
       <c r="B4" t="n">
-        <v>101257</v>
+        <v>106484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221223</v>
+        <v>1897</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711778</v>
+        <v>711803</v>
       </c>
       <c r="R4" t="n">
-        <v>6374934</v>
+        <v>6374919</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,6 +979,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121573221</v>
+        <v>121573226</v>
       </c>
       <c r="B5" t="n">
-        <v>103629</v>
+        <v>108728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220164</v>
+        <v>220204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711803</v>
+        <v>711891</v>
       </c>
       <c r="R5" t="n">
-        <v>6374919</v>
+        <v>6375090</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121573222</v>
+        <v>121573227</v>
       </c>
       <c r="B6" t="n">
-        <v>106483</v>
+        <v>103630</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1897</v>
+        <v>220164</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1162,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711803</v>
+        <v>711891</v>
       </c>
       <c r="R6" t="n">
-        <v>6374919</v>
+        <v>6375090</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,11 +1198,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>1984-08-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121573224</v>
+        <v>121573221</v>
       </c>
       <c r="B7" t="n">
-        <v>103025</v>
+        <v>103630</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,25 +1241,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222002</v>
+        <v>220164</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711813</v>
+        <v>711803</v>
       </c>
       <c r="R7" t="n">
-        <v>6374960</v>
+        <v>6374919</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121573226</v>
+        <v>121573223</v>
       </c>
       <c r="B8" t="n">
-        <v>108727</v>
+        <v>101258</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,21 +1352,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220204</v>
+        <v>221223</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711891</v>
+        <v>711808</v>
       </c>
       <c r="R8" t="n">
-        <v>6375090</v>
+        <v>6374924</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121573223</v>
+        <v>121573220</v>
       </c>
       <c r="B9" t="n">
-        <v>101257</v>
+        <v>101258</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711808</v>
+        <v>711778</v>
       </c>
       <c r="R9" t="n">
-        <v>6374924</v>
+        <v>6374934</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121573222</v>
+        <v>121573221</v>
       </c>
       <c r="B4" t="n">
-        <v>106484</v>
+        <v>103630</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1897</v>
+        <v>220164</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,7 +949,7 @@
         <v>6374919</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,11 +979,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>1984-08-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121573226</v>
+        <v>121573227</v>
       </c>
       <c r="B5" t="n">
-        <v>108728</v>
+        <v>103630</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1026,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220204</v>
+        <v>220164</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1122,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121573227</v>
+        <v>121573220</v>
       </c>
       <c r="B6" t="n">
-        <v>103630</v>
+        <v>101258</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220164</v>
+        <v>221223</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711891</v>
+        <v>711778</v>
       </c>
       <c r="R6" t="n">
-        <v>6375090</v>
+        <v>6374934</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121573221</v>
+        <v>121573222</v>
       </c>
       <c r="B7" t="n">
-        <v>103630</v>
+        <v>106484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220164</v>
+        <v>1897</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,7 +1270,7 @@
         <v>6374919</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,6 +1300,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121573220</v>
+        <v>121573226</v>
       </c>
       <c r="B9" t="n">
-        <v>101258</v>
+        <v>108728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221223</v>
+        <v>220204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711778</v>
+        <v>711891</v>
       </c>
       <c r="R9" t="n">
-        <v>6374934</v>
+        <v>6375090</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,6 +1547,651 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121608934</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80276</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>737</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kraterlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Gyalecta truncigena</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Hepp</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>711840</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6375057</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Betad ekdominerad ädellövsskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>lundalm</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121608945</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80277</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>738</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Almlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Gyalecta ulmi</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>711840</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6375057</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Betad ekdominerad ädellövsskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>lundalm</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121608950</v>
+      </c>
+      <c r="B12" t="n">
+        <v>84889</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>233051</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Amphisphaeria umbrina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) De Not.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>711840</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6375057</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Betad ekdominerad ädellövsskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>lundalm</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121608891</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80276</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>737</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kraterlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Gyalecta truncigena</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Hepp</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>711853</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6375112</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Betad ekdominerad ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121608918</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90709</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>884</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pälsticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Inonotus hispidus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Bull.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>711853</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6375112</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Betad ekdominerad ädellövsskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121573224</v>
+        <v>121573227</v>
       </c>
       <c r="B3" t="n">
-        <v>103026</v>
+        <v>103630</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222002</v>
+        <v>220164</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711813</v>
+        <v>711891</v>
       </c>
       <c r="R3" t="n">
-        <v>6374960</v>
+        <v>6375090</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121573221</v>
+        <v>121573223</v>
       </c>
       <c r="B4" t="n">
-        <v>103630</v>
+        <v>101258</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220164</v>
+        <v>221223</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711803</v>
+        <v>711808</v>
       </c>
       <c r="R4" t="n">
-        <v>6374919</v>
+        <v>6374924</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121573227</v>
+        <v>121573224</v>
       </c>
       <c r="B5" t="n">
-        <v>103630</v>
+        <v>103026</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1022,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220164</v>
+        <v>222002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711891</v>
+        <v>711813</v>
       </c>
       <c r="R5" t="n">
-        <v>6375090</v>
+        <v>6374960</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121573220</v>
+        <v>121573221</v>
       </c>
       <c r="B6" t="n">
-        <v>101258</v>
+        <v>103630</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1133,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221223</v>
+        <v>220164</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711778</v>
+        <v>711803</v>
       </c>
       <c r="R6" t="n">
-        <v>6374934</v>
+        <v>6374919</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121573223</v>
+        <v>121573226</v>
       </c>
       <c r="B8" t="n">
-        <v>101258</v>
+        <v>108728</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,21 +1352,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221223</v>
+        <v>220204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711808</v>
+        <v>711891</v>
       </c>
       <c r="R8" t="n">
-        <v>6374924</v>
+        <v>6375090</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121573226</v>
+        <v>121573220</v>
       </c>
       <c r="B9" t="n">
-        <v>108728</v>
+        <v>101258</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220204</v>
+        <v>221223</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711891</v>
+        <v>711778</v>
       </c>
       <c r="R9" t="n">
-        <v>6375090</v>
+        <v>6374934</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121608934</v>
+        <v>121608891</v>
       </c>
       <c r="B10" t="n">
         <v>80276</v>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711840</v>
+        <v>711853</v>
       </c>
       <c r="R10" t="n">
-        <v>6375057</v>
+        <v>6375112</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövsskog</t>
+          <t>Betad ekdominerad ädellövskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>lundalm</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121608945</v>
+        <v>121608934</v>
       </c>
       <c r="B11" t="n">
-        <v>80277</v>
+        <v>80276</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Ach.) Hepp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121608891</v>
+        <v>121608918</v>
       </c>
       <c r="B13" t="n">
-        <v>80276</v>
+        <v>90709</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,30 +1947,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>737</v>
+        <v>884</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Pälsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Inonotus hispidus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Bull.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2028,7 +2032,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövskog</t>
+          <t>Betad ekdominerad ädellövsskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2061,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121608918</v>
+        <v>121608945</v>
       </c>
       <c r="B14" t="n">
-        <v>90709</v>
+        <v>80277</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,34 +2081,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>884</v>
+        <v>738</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pälsticka</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Inonotus hispidus</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bull.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711853</v>
+        <v>711840</v>
       </c>
       <c r="R14" t="n">
-        <v>6375112</v>
+        <v>6375057</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,17 +2167,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>lundalm</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121573227</v>
+        <v>121573222</v>
       </c>
       <c r="B3" t="n">
-        <v>103630</v>
+        <v>106484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220164</v>
+        <v>1897</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711891</v>
+        <v>711803</v>
       </c>
       <c r="R3" t="n">
-        <v>6375090</v>
+        <v>6374919</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,6 +872,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121573223</v>
+        <v>121573221</v>
       </c>
       <c r="B4" t="n">
-        <v>101258</v>
+        <v>103630</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221223</v>
+        <v>220164</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711808</v>
+        <v>711803</v>
       </c>
       <c r="R4" t="n">
-        <v>6374924</v>
+        <v>6374919</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121573224</v>
+        <v>121573226</v>
       </c>
       <c r="B5" t="n">
-        <v>103026</v>
+        <v>108728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,20 +1027,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222002</v>
+        <v>220204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1050,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711813</v>
+        <v>711891</v>
       </c>
       <c r="R5" t="n">
-        <v>6374960</v>
+        <v>6375090</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121573221</v>
+        <v>121573227</v>
       </c>
       <c r="B6" t="n">
         <v>103630</v>
@@ -1157,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711803</v>
+        <v>711891</v>
       </c>
       <c r="R6" t="n">
-        <v>6374919</v>
+        <v>6375090</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1224,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121573222</v>
+        <v>121573220</v>
       </c>
       <c r="B7" t="n">
-        <v>106484</v>
+        <v>101258</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1897</v>
+        <v>221223</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711803</v>
+        <v>711778</v>
       </c>
       <c r="R7" t="n">
-        <v>6374919</v>
+        <v>6374934</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,11 +1305,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>1984-08-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121573226</v>
+        <v>121573224</v>
       </c>
       <c r="B8" t="n">
-        <v>108728</v>
+        <v>103026</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,20 +1348,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220204</v>
+        <v>222002</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711891</v>
+        <v>711813</v>
       </c>
       <c r="R8" t="n">
-        <v>6375090</v>
+        <v>6374960</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121573220</v>
+        <v>121573223</v>
       </c>
       <c r="B9" t="n">
         <v>101258</v>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711778</v>
+        <v>711808</v>
       </c>
       <c r="R9" t="n">
-        <v>6374934</v>
+        <v>6374924</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121608891</v>
+        <v>121608934</v>
       </c>
       <c r="B10" t="n">
         <v>80276</v>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711853</v>
+        <v>711840</v>
       </c>
       <c r="R10" t="n">
-        <v>6375112</v>
+        <v>6375057</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövskog</t>
+          <t>Betad ekdominerad ädellövsskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>lundalm</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121608934</v>
+        <v>121608918</v>
       </c>
       <c r="B11" t="n">
-        <v>80276</v>
+        <v>90709</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,30 +1696,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>737</v>
+        <v>884</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Pälsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Inonotus hispidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Bull.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1727,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711840</v>
+        <v>711853</v>
       </c>
       <c r="R11" t="n">
-        <v>6375057</v>
+        <v>6375112</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,17 +1786,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>lundalm</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1810,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121608950</v>
+        <v>121608945</v>
       </c>
       <c r="B12" t="n">
-        <v>84889</v>
+        <v>80277</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1822,25 +1826,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>233051</v>
+        <v>738</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Almlav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Amphisphaeria umbrina</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) De Not.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1931,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121608918</v>
+        <v>121608891</v>
       </c>
       <c r="B13" t="n">
-        <v>90709</v>
+        <v>80276</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,34 +1960,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>884</v>
+        <v>737</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pälsticka</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Inonotus hispidus</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bull.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>(Ach.) Hepp</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2032,7 +2041,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövsskog</t>
+          <t>Betad ekdominerad ädellövskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2065,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121608945</v>
+        <v>121608950</v>
       </c>
       <c r="B14" t="n">
-        <v>80277</v>
+        <v>84889</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,34 +2086,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>738</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Almlav</t>
-        </is>
+        <v>233051</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Amphisphaeria umbrina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Fr.) De Not.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121573223</v>
+        <v>121573227</v>
       </c>
       <c r="B3" t="n">
-        <v>101266</v>
+        <v>103638</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221223</v>
+        <v>220164</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711808</v>
+        <v>711891</v>
       </c>
       <c r="R3" t="n">
-        <v>6374924</v>
+        <v>6375090</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121573224</v>
+        <v>121573222</v>
       </c>
       <c r="B4" t="n">
-        <v>103034</v>
+        <v>106492</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,20 +915,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222002</v>
+        <v>1897</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711813</v>
+        <v>711803</v>
       </c>
       <c r="R4" t="n">
-        <v>6374960</v>
+        <v>6374919</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,6 +979,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121573226</v>
+        <v>121573224</v>
       </c>
       <c r="B5" t="n">
-        <v>108736</v>
+        <v>103034</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,20 +1027,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220204</v>
+        <v>222002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1050,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711891</v>
+        <v>711813</v>
       </c>
       <c r="R5" t="n">
-        <v>6375090</v>
+        <v>6374960</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121573221</v>
+        <v>121573226</v>
       </c>
       <c r="B6" t="n">
-        <v>103638</v>
+        <v>108736</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220164</v>
+        <v>220204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1157,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711803</v>
+        <v>711891</v>
       </c>
       <c r="R6" t="n">
-        <v>6374919</v>
+        <v>6375090</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1224,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121573222</v>
+        <v>121573223</v>
       </c>
       <c r="B7" t="n">
-        <v>106492</v>
+        <v>101266</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1897</v>
+        <v>221223</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711803</v>
+        <v>711808</v>
       </c>
       <c r="R7" t="n">
-        <v>6374919</v>
+        <v>6374924</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,11 +1305,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>1984-08-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121573227</v>
+        <v>121573220</v>
       </c>
       <c r="B8" t="n">
-        <v>103638</v>
+        <v>101266</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,21 +1352,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220164</v>
+        <v>221223</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711891</v>
+        <v>711778</v>
       </c>
       <c r="R8" t="n">
-        <v>6375090</v>
+        <v>6374934</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121573220</v>
+        <v>121573221</v>
       </c>
       <c r="B9" t="n">
-        <v>101266</v>
+        <v>103638</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221223</v>
+        <v>220164</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711778</v>
+        <v>711803</v>
       </c>
       <c r="R9" t="n">
-        <v>6374934</v>
+        <v>6374919</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121608918</v>
+        <v>121608950</v>
       </c>
       <c r="B10" t="n">
-        <v>90717</v>
+        <v>84896</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,37 +1562,24 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>884</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Pälsticka</t>
-        </is>
+        <v>233051</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Inonotus hispidus</t>
+          <t>Amphisphaeria umbrina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bull.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) De Not.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1601,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711853</v>
+        <v>711840</v>
       </c>
       <c r="R10" t="n">
-        <v>6375112</v>
+        <v>6375057</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,17 +1643,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>lundalm</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1684,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121608950</v>
+        <v>121608945</v>
       </c>
       <c r="B11" t="n">
-        <v>84896</v>
+        <v>80284</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1696,25 +1683,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>233051</v>
+        <v>738</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Almlav</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Amphisphaeria umbrina</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) De Not.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1935,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121608945</v>
+        <v>121608934</v>
       </c>
       <c r="B13" t="n">
-        <v>80284</v>
+        <v>80283</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Ach.) Hepp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2065,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121608934</v>
+        <v>121608918</v>
       </c>
       <c r="B14" t="n">
-        <v>80283</v>
+        <v>90717</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,30 +2077,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>737</v>
+        <v>884</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Pälsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Inonotus hispidus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Bull.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711840</v>
+        <v>711853</v>
       </c>
       <c r="R14" t="n">
-        <v>6375057</v>
+        <v>6375112</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,17 +2167,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>lundalm</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121573227</v>
+        <v>121573221</v>
       </c>
       <c r="B3" t="n">
         <v>103638</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711891</v>
+        <v>711803</v>
       </c>
       <c r="R3" t="n">
-        <v>6375090</v>
+        <v>6374919</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121573222</v>
+        <v>121573223</v>
       </c>
       <c r="B4" t="n">
-        <v>106492</v>
+        <v>101266</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1897</v>
+        <v>221223</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711803</v>
+        <v>711808</v>
       </c>
       <c r="R4" t="n">
-        <v>6374919</v>
+        <v>6374924</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,11 +979,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>1984-08-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1122,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121573226</v>
+        <v>121573222</v>
       </c>
       <c r="B6" t="n">
-        <v>108736</v>
+        <v>106492</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,16 +1133,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220204</v>
+        <v>1897</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1162,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711891</v>
+        <v>711803</v>
       </c>
       <c r="R6" t="n">
-        <v>6375090</v>
+        <v>6374919</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,6 +1193,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1229,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121573223</v>
+        <v>121573220</v>
       </c>
       <c r="B7" t="n">
         <v>101266</v>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711808</v>
+        <v>711778</v>
       </c>
       <c r="R7" t="n">
-        <v>6374924</v>
+        <v>6374934</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121573220</v>
+        <v>121573226</v>
       </c>
       <c r="B8" t="n">
-        <v>101266</v>
+        <v>108736</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,21 +1352,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221223</v>
+        <v>220204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711778</v>
+        <v>711891</v>
       </c>
       <c r="R8" t="n">
-        <v>6374934</v>
+        <v>6375090</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121573221</v>
+        <v>121573227</v>
       </c>
       <c r="B9" t="n">
         <v>103638</v>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711803</v>
+        <v>711891</v>
       </c>
       <c r="R9" t="n">
-        <v>6374919</v>
+        <v>6375090</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121608950</v>
+        <v>121608934</v>
       </c>
       <c r="B10" t="n">
-        <v>84896</v>
+        <v>80283</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,25 +1562,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>233051</v>
+        <v>737</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kraterlav</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Amphisphaeria umbrina</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) De Not.</t>
+          <t>(Ach.) Hepp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1671,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121608945</v>
+        <v>121608891</v>
       </c>
       <c r="B11" t="n">
-        <v>80284</v>
+        <v>80283</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1687,21 +1696,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Ach.) Hepp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711840</v>
+        <v>711853</v>
       </c>
       <c r="R11" t="n">
-        <v>6375057</v>
+        <v>6375112</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,22 +1777,22 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövsskog</t>
+          <t>Betad ekdominerad ädellövskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>lundalm</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1801,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121608891</v>
+        <v>121608918</v>
       </c>
       <c r="B12" t="n">
-        <v>80283</v>
+        <v>90717</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,30 +1826,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>737</v>
+        <v>884</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Pälsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Inonotus hispidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Bull.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1898,7 +1911,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövskog</t>
+          <t>Betad ekdominerad ädellövsskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -1931,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121608934</v>
+        <v>121608945</v>
       </c>
       <c r="B13" t="n">
-        <v>80283</v>
+        <v>80284</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,21 +1960,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2061,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121608918</v>
+        <v>121608950</v>
       </c>
       <c r="B14" t="n">
-        <v>90717</v>
+        <v>84896</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2073,37 +2086,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>884</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Pälsticka</t>
-        </is>
+        <v>233051</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Inonotus hispidus</t>
+          <t>Amphisphaeria umbrina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bull.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) De Not.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711853</v>
+        <v>711840</v>
       </c>
       <c r="R14" t="n">
-        <v>6375112</v>
+        <v>6375057</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,17 +2167,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>lundalm</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121573224</v>
+        <v>121573226</v>
       </c>
       <c r="B5" t="n">
-        <v>103034</v>
+        <v>108736</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222002</v>
+        <v>220204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711813</v>
+        <v>711891</v>
       </c>
       <c r="R5" t="n">
-        <v>6374960</v>
+        <v>6375090</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121573222</v>
+        <v>121573224</v>
       </c>
       <c r="B6" t="n">
-        <v>106492</v>
+        <v>103034</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,20 +1129,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1897</v>
+        <v>222002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711803</v>
+        <v>711813</v>
       </c>
       <c r="R6" t="n">
-        <v>6374919</v>
+        <v>6374960</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,11 +1193,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>1984-08-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121573220</v>
+        <v>121573227</v>
       </c>
       <c r="B7" t="n">
-        <v>101266</v>
+        <v>103638</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1240,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221223</v>
+        <v>220164</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711778</v>
+        <v>711891</v>
       </c>
       <c r="R7" t="n">
-        <v>6374934</v>
+        <v>6375090</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121573226</v>
+        <v>121573222</v>
       </c>
       <c r="B8" t="n">
-        <v>108736</v>
+        <v>106492</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,16 +1347,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220204</v>
+        <v>1897</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1376,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711891</v>
+        <v>711803</v>
       </c>
       <c r="R8" t="n">
-        <v>6375090</v>
+        <v>6374919</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,6 +1407,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121573227</v>
+        <v>121573220</v>
       </c>
       <c r="B9" t="n">
-        <v>103638</v>
+        <v>101266</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220164</v>
+        <v>221223</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711891</v>
+        <v>711778</v>
       </c>
       <c r="R9" t="n">
-        <v>6375090</v>
+        <v>6374934</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121608934</v>
+        <v>121608918</v>
       </c>
       <c r="B10" t="n">
-        <v>80283</v>
+        <v>90717</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,30 +1566,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>737</v>
+        <v>884</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Pälsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Inonotus hispidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Bull.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1597,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711840</v>
+        <v>711853</v>
       </c>
       <c r="R10" t="n">
-        <v>6375057</v>
+        <v>6375112</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1652,17 +1656,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>lundalm</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1680,7 +1684,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121608891</v>
+        <v>121608934</v>
       </c>
       <c r="B11" t="n">
         <v>80283</v>
@@ -1727,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711853</v>
+        <v>711840</v>
       </c>
       <c r="R11" t="n">
-        <v>6375112</v>
+        <v>6375057</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,22 +1781,22 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövskog</t>
+          <t>Betad ekdominerad ädellövsskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>lundalm</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1810,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121608918</v>
+        <v>121608945</v>
       </c>
       <c r="B12" t="n">
-        <v>90717</v>
+        <v>80284</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,34 +1830,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>884</v>
+        <v>738</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pälsticka</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Inonotus hispidus</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bull.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711853</v>
+        <v>711840</v>
       </c>
       <c r="R12" t="n">
-        <v>6375112</v>
+        <v>6375057</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,17 +1916,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>lundalm</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121608945</v>
+        <v>121608891</v>
       </c>
       <c r="B13" t="n">
-        <v>80284</v>
+        <v>80283</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Ach.) Hepp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711840</v>
+        <v>711853</v>
       </c>
       <c r="R13" t="n">
-        <v>6375057</v>
+        <v>6375112</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,22 +2041,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövsskog</t>
+          <t>Betad ekdominerad ädellövskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>lundalm</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121573221</v>
+        <v>121573226</v>
       </c>
       <c r="B3" t="n">
-        <v>103638</v>
+        <v>108736</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220164</v>
+        <v>220204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711803</v>
+        <v>711891</v>
       </c>
       <c r="R3" t="n">
-        <v>6374919</v>
+        <v>6375090</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121573223</v>
+        <v>121573220</v>
       </c>
       <c r="B4" t="n">
         <v>101266</v>
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711808</v>
+        <v>711778</v>
       </c>
       <c r="R4" t="n">
-        <v>6374924</v>
+        <v>6374934</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121573226</v>
+        <v>121573224</v>
       </c>
       <c r="B5" t="n">
-        <v>108736</v>
+        <v>103034</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,20 +1022,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220204</v>
+        <v>222002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711891</v>
+        <v>711813</v>
       </c>
       <c r="R5" t="n">
-        <v>6375090</v>
+        <v>6374960</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121573224</v>
+        <v>121573222</v>
       </c>
       <c r="B6" t="n">
-        <v>103034</v>
+        <v>106492</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,20 +1129,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222002</v>
+        <v>1897</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711813</v>
+        <v>711803</v>
       </c>
       <c r="R6" t="n">
-        <v>6374960</v>
+        <v>6374919</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,6 +1193,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121573227</v>
+        <v>121573223</v>
       </c>
       <c r="B7" t="n">
-        <v>103638</v>
+        <v>101266</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220164</v>
+        <v>221223</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,13 +1269,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711891</v>
+        <v>711808</v>
       </c>
       <c r="R7" t="n">
-        <v>6375090</v>
+        <v>6374924</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121573222</v>
+        <v>121573221</v>
       </c>
       <c r="B8" t="n">
-        <v>106492</v>
+        <v>103638</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1352,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1897</v>
+        <v>220164</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,7 +1382,7 @@
         <v>6374919</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,11 +1412,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>1984-08-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121573220</v>
+        <v>121573227</v>
       </c>
       <c r="B9" t="n">
-        <v>101266</v>
+        <v>103638</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221223</v>
+        <v>220164</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711778</v>
+        <v>711891</v>
       </c>
       <c r="R9" t="n">
-        <v>6374934</v>
+        <v>6375090</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121608918</v>
+        <v>121608945</v>
       </c>
       <c r="B10" t="n">
-        <v>90717</v>
+        <v>80284</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,34 +1566,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>884</v>
+        <v>738</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pälsticka</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Inonotus hispidus</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bull.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>(Sw.) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1601,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711853</v>
+        <v>711840</v>
       </c>
       <c r="R10" t="n">
-        <v>6375112</v>
+        <v>6375057</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1656,17 +1652,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>lundalm</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1814,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121608945</v>
+        <v>121608950</v>
       </c>
       <c r="B12" t="n">
-        <v>80284</v>
+        <v>84896</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,34 +1822,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>738</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Almlav</t>
-        </is>
+        <v>233051</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Amphisphaeria umbrina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Fr.) De Not.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2074,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121608950</v>
+        <v>121608918</v>
       </c>
       <c r="B14" t="n">
-        <v>84896</v>
+        <v>90717</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,24 +2073,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>233051</v>
+        <v>884</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pälsticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Amphisphaeria umbrina</t>
+          <t>Inonotus hispidus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) De Not.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Bull.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711840</v>
+        <v>711853</v>
       </c>
       <c r="R14" t="n">
-        <v>6375057</v>
+        <v>6375112</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,17 +2167,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>lundalm</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121573226</v>
+        <v>121573223</v>
       </c>
       <c r="B3" t="n">
-        <v>108736</v>
+        <v>101266</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220204</v>
+        <v>221223</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711891</v>
+        <v>711808</v>
       </c>
       <c r="R3" t="n">
-        <v>6375090</v>
+        <v>6374924</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121573224</v>
+        <v>121573221</v>
       </c>
       <c r="B5" t="n">
-        <v>103034</v>
+        <v>103638</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1022,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222002</v>
+        <v>220164</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711813</v>
+        <v>711803</v>
       </c>
       <c r="R5" t="n">
-        <v>6374960</v>
+        <v>6374919</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1117,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121573222</v>
+        <v>121573226</v>
       </c>
       <c r="B6" t="n">
-        <v>106492</v>
+        <v>108736</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,16 +1133,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1897</v>
+        <v>220204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711803</v>
+        <v>711891</v>
       </c>
       <c r="R6" t="n">
-        <v>6374919</v>
+        <v>6375090</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,11 +1193,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>1984-08-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121573223</v>
+        <v>121573224</v>
       </c>
       <c r="B7" t="n">
-        <v>101266</v>
+        <v>103034</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,25 +1236,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221223</v>
+        <v>222002</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711808</v>
+        <v>711813</v>
       </c>
       <c r="R7" t="n">
-        <v>6374924</v>
+        <v>6374960</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121573221</v>
+        <v>121573227</v>
       </c>
       <c r="B8" t="n">
         <v>103638</v>
@@ -1376,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711803</v>
+        <v>711891</v>
       </c>
       <c r="R8" t="n">
-        <v>6374919</v>
+        <v>6375090</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1443,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121573227</v>
+        <v>121573222</v>
       </c>
       <c r="B9" t="n">
-        <v>103638</v>
+        <v>106492</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220164</v>
+        <v>1897</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,13 +1478,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711891</v>
+        <v>711803</v>
       </c>
       <c r="R9" t="n">
-        <v>6375090</v>
+        <v>6374919</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,6 +1514,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121608945</v>
+        <v>121608891</v>
       </c>
       <c r="B10" t="n">
-        <v>80284</v>
+        <v>80283</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,21 +1566,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(Ach.) Hepp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711840</v>
+        <v>711853</v>
       </c>
       <c r="R10" t="n">
-        <v>6375057</v>
+        <v>6375112</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövsskog</t>
+          <t>Betad ekdominerad ädellövskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>lundalm</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121608891</v>
+        <v>121608945</v>
       </c>
       <c r="B13" t="n">
-        <v>80283</v>
+        <v>80284</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711853</v>
+        <v>711840</v>
       </c>
       <c r="R13" t="n">
-        <v>6375112</v>
+        <v>6375057</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,22 +2028,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövskog</t>
+          <t>Betad ekdominerad ädellövsskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>lundalm</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121573223</v>
+        <v>121573222</v>
       </c>
       <c r="B3" t="n">
-        <v>101266</v>
+        <v>106492</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221223</v>
+        <v>1897</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711808</v>
+        <v>711803</v>
       </c>
       <c r="R3" t="n">
-        <v>6374924</v>
+        <v>6374919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,6 +872,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1331,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121573227</v>
+        <v>121573223</v>
       </c>
       <c r="B8" t="n">
-        <v>103638</v>
+        <v>101266</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1352,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220164</v>
+        <v>221223</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,13 +1376,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711891</v>
+        <v>711808</v>
       </c>
       <c r="R8" t="n">
-        <v>6375090</v>
+        <v>6374924</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121573222</v>
+        <v>121573227</v>
       </c>
       <c r="B9" t="n">
-        <v>106492</v>
+        <v>103638</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1897</v>
+        <v>220164</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,13 +1483,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711803</v>
+        <v>711891</v>
       </c>
       <c r="R9" t="n">
-        <v>6374919</v>
+        <v>6375090</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1514,11 +1519,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>1984-08-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121608891</v>
+        <v>121608950</v>
       </c>
       <c r="B10" t="n">
-        <v>80283</v>
+        <v>84896</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,34 +1562,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>737</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Mörk kraterlav</t>
-        </is>
+        <v>233051</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Amphisphaeria umbrina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
+          <t>(Fr.) De Not.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1597,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711853</v>
+        <v>711840</v>
       </c>
       <c r="R10" t="n">
-        <v>6375112</v>
+        <v>6375057</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1647,22 +1638,22 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövskog</t>
+          <t>Betad ekdominerad ädellövsskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>lundalm</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1810,10 +1801,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121608950</v>
+        <v>121608891</v>
       </c>
       <c r="B12" t="n">
-        <v>84896</v>
+        <v>80283</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1822,25 +1813,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>233051</v>
+        <v>737</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mörk kraterlav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Amphisphaeria umbrina</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) De Not.</t>
+          <t>(Ach.) Hepp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1848,10 +1848,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711840</v>
+        <v>711853</v>
       </c>
       <c r="R12" t="n">
-        <v>6375057</v>
+        <v>6375112</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,22 +1898,22 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövsskog</t>
+          <t>Betad ekdominerad ädellövskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>lundalm</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>105074320</v>
       </c>
       <c r="B2" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711803.3279234773</v>
+        <v>711803</v>
       </c>
       <c r="R2" t="n">
-        <v>6374929.504835613</v>
+        <v>6374930</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>1984-06-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1984-06-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074320</v>
       </c>
       <c r="B2" t="n">
-        <v>101649</v>
+        <v>101657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074320</v>
       </c>
       <c r="B2" t="n">
-        <v>101657</v>
+        <v>101662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074320</v>
       </c>
       <c r="B2" t="n">
-        <v>101662</v>
+        <v>101668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074320</v>
       </c>
       <c r="B2" t="n">
-        <v>101668</v>
+        <v>101669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074320</v>
       </c>
       <c r="B2" t="n">
-        <v>101669</v>
+        <v>101696</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074320</v>
       </c>
       <c r="B2" t="n">
-        <v>101696</v>
+        <v>101702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074320</v>
       </c>
       <c r="B2" t="n">
-        <v>101702</v>
+        <v>101709</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074320</v>
       </c>
       <c r="B2" t="n">
-        <v>101709</v>
+        <v>101713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074320</v>
       </c>
       <c r="B2" t="n">
-        <v>101713</v>
+        <v>101720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074320</v>
       </c>
       <c r="B2" t="n">
-        <v>101723</v>
+        <v>101728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>105074320</v>
       </c>
       <c r="B2" t="n">
-        <v>101728</v>
+        <v>101736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105074320</v>
+        <v>121608891</v>
       </c>
       <c r="B2" t="n">
-        <v>101736</v>
+        <v>81024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221223</v>
+        <v>737</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Ach.) Hepp</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gandarve 700 m ONO, Gtl</t>
+          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711803</v>
+        <v>711853</v>
       </c>
       <c r="R2" t="n">
-        <v>6374930</v>
+        <v>6375112</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1984-06-21</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1984-06-21</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,80 +761,94 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lövskog.</t>
+          <t>Betad ekdominerad ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Dennis Nyström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121573221</v>
+        <v>121608934</v>
       </c>
       <c r="B3" t="n">
-        <v>103656</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220164</v>
+        <v>737</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Ach.) Hepp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711803</v>
+        <v>711840</v>
       </c>
       <c r="R3" t="n">
-        <v>6374919</v>
+        <v>6375057</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1984-06-21</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1984-08-10</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,76 +886,94 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Ädellövskog med fuktområde.</t>
+          <t>Betad ekdominerad ädellövsskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>lundalm</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121573227</v>
+        <v>121608945</v>
       </c>
       <c r="B4" t="n">
-        <v>103656</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81025</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220164</v>
+        <v>738</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Almlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Gyalecta ulmi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Sw.) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>711891</v>
+        <v>711840</v>
       </c>
       <c r="R4" t="n">
-        <v>6375090</v>
+        <v>6375057</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,12 +997,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1984-06-21</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1984-08-10</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,73 +1011,95 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Ädellövskog med fuktområde.</t>
+          <t>Betad ekdominerad ädellövsskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>lundalm</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121573222</v>
+        <v>121608918</v>
       </c>
       <c r="B5" t="n">
-        <v>106510</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1897</v>
+        <v>884</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korskovall</t>
+          <t>Pälsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Melampyrum cristatum</t>
+          <t>Inonotus hispidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Bull.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>711803</v>
+        <v>711853</v>
       </c>
       <c r="R5" t="n">
-        <v>6374919</v>
+        <v>6375112</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,17 +1126,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1984-06-21</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1984-08-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spridd 25 m mot NV.</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,38 +1140,49 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Ädellövskog med fuktområde.</t>
+          <t>Betad ekdominerad ädellövsskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121573220</v>
+        <v>121573222</v>
       </c>
       <c r="B6" t="n">
-        <v>101284</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,21 +1190,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221223</v>
+        <v>1897</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Korskovall</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Melampyrum cristatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>711778</v>
+        <v>711803</v>
       </c>
       <c r="R6" t="n">
-        <v>6374934</v>
+        <v>6374919</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,6 +1250,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spridd 25 m mot NV.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,15 +1286,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121573223</v>
+        <v>121608804</v>
       </c>
       <c r="B7" t="n">
-        <v>101284</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,34 +1297,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221223</v>
+        <v>102468</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Korkmusslingsmal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Nemapogon fungivorellus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Benander, 1939)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>insamlad för uppfödning/kläckning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>711808</v>
+        <v>711926</v>
       </c>
       <c r="R7" t="n">
-        <v>6374924</v>
+        <v>6375088</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,12 +1364,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1984-06-21</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1984-08-10</t>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar av korkmussling med gnagspår insamlade för uppfödning/kläckning. Ny för Gotland om det visar sig vara den aktuella arten, men både punktsvampmal M. tessulatella och tiggarsvampmal A. mendicella är andra tänkbara alternativ. Två korkmusslingsmalar framkläckta 23 februari 2025 ur de fruktrkoppar som insamlades.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,60 +1383,76 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Ädellövskog med fuktområde.</t>
+          <t>Betad ekdominerad ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>korkmussling</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fomitopsis quercina</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Fomitopsis quercina</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121573226</v>
+        <v>121573231</v>
       </c>
       <c r="B8" t="n">
-        <v>108754</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220204</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1462,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>711891</v>
+        <v>711852</v>
       </c>
       <c r="R8" t="n">
-        <v>6375090</v>
+        <v>6375010</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1428,15 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121573224</v>
+        <v>121573248</v>
       </c>
       <c r="B9" t="n">
-        <v>103052</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,21 +1540,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222002</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1468,10 +1564,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>711813</v>
+        <v>711921</v>
       </c>
       <c r="R9" t="n">
-        <v>6374960</v>
+        <v>6375120</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1535,60 +1631,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121608891</v>
+        <v>121573232</v>
       </c>
       <c r="B10" t="n">
-        <v>80296</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>737</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>711853</v>
+        <v>711852</v>
       </c>
       <c r="R10" t="n">
-        <v>6375112</v>
+        <v>6375010</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1612,12 +1696,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>1984-06-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>1984-08-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,100 +1710,68 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ädellövskog med fuktområde.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121608918</v>
+        <v>121573235</v>
       </c>
       <c r="B11" t="n">
-        <v>90731</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>884</v>
+        <v>219864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pälsticka</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inonotus hispidus</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bull.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>711853</v>
+        <v>711926</v>
       </c>
       <c r="R11" t="n">
-        <v>6375112</v>
+        <v>6375111</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1746,12 +1798,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>1984-06-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>1984-08-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,90 +1812,71 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövsskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ädellövskog med fuktområde.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121608950</v>
+        <v>121573228</v>
       </c>
       <c r="B12" t="n">
-        <v>84910</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>233051</v>
+        <v>220103</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Amphisphaeria umbrina</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) De Not.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>711840</v>
+        <v>711911</v>
       </c>
       <c r="R12" t="n">
-        <v>6375057</v>
+        <v>6375091</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1867,12 +1900,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>1984-06-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>1984-08-10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,96 +1914,68 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövsskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>lundalm</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Ulmus minor</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Ulmus minor</t>
+          <t>Ädellövskog med fuktområde.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121608945</v>
+        <v>121573236</v>
       </c>
       <c r="B13" t="n">
-        <v>80297</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>738</v>
+        <v>220103</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Almlav</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gyalecta ulmi</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sw.) Zahlbr.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>711840</v>
+        <v>711926</v>
       </c>
       <c r="R13" t="n">
-        <v>6375057</v>
+        <v>6375111</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,12 +2002,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>1984-06-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>1984-08-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2011,99 +2016,71 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövsskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>lundalm</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Ulmus minor</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Ulmus minor</t>
+          <t>Ädellövskog med fuktområde.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121608934</v>
+        <v>121573221</v>
       </c>
       <c r="B14" t="n">
-        <v>80296</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>737</v>
+        <v>220164</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kraterlav</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gyalecta truncigena</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Hepp</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>711840</v>
+        <v>711803</v>
       </c>
       <c r="R14" t="n">
-        <v>6375057</v>
+        <v>6374919</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2127,12 +2104,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>1984-06-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>1984-08-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,42 +2118,1578 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Betad ekdominerad ädellövsskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>lundalm</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Ulmus minor</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Ulmus minor</t>
+          <t>Ädellövskog med fuktområde.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121573227</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>711891</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6375090</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121573226</v>
+      </c>
+      <c r="B16" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>711891</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6375090</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121573233</v>
+      </c>
+      <c r="B17" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>711852</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6375010</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121573244</v>
+      </c>
+      <c r="B18" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>711921</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6375120</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121573250</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>711921</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6375120</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>105074319</v>
+      </c>
+      <c r="B20" t="n">
+        <v>102225</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gandarve 700 m ONO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>711803</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6374930</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1989-12-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Lövskog nära åkerhörn, relativt torr</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121573220</v>
+      </c>
+      <c r="B21" t="n">
+        <v>102225</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>711778</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6374934</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121573223</v>
+      </c>
+      <c r="B22" t="n">
+        <v>102225</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>711808</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6374924</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121573230</v>
+      </c>
+      <c r="B23" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>711852</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6375010</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121573246</v>
+      </c>
+      <c r="B24" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>711921</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6375120</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121573218</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>711862</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6375020</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>105074309</v>
+      </c>
+      <c r="B26" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gandarve 800 m ONO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>711852</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6374960</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>1989-12-31</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Lövskog vid stig</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121573219</v>
+      </c>
+      <c r="B27" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>711743</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6374939</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121573224</v>
+      </c>
+      <c r="B28" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vänge Norrbys 1:12 3, Gandarve 700 m NO, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>711813</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6374960</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>1984-06-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>1984-08-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Ädellövskog med fuktområde.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121608950</v>
+      </c>
+      <c r="B29" t="n">
+        <v>85908</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>233051</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Amphisphaeria umbrina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) De Not.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vänge, Norrbys 1:12 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>711840</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6375057</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Betad ekdominerad ädellövsskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>lundalm</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
           <t>Dennis Nyström</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>Dennis Nyström</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59132-2024 artfynd.xlsx
+++ b/artfynd/A 59132-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121608891</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121608934</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121608945</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121608918</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1283,6 +1308,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573222</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1424,6 +1454,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121608804</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1526,6 +1561,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573231</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1628,6 +1668,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573248</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1730,6 +1775,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573232</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573235</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1934,6 +1989,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573228</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2036,6 +2096,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573236</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2138,6 +2203,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573221</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2240,6 +2310,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573227</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2342,6 +2417,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573226</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2444,6 +2524,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573233</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2546,6 +2631,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573244</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2648,6 +2738,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573250</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2754,6 +2849,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074319</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2856,6 +2956,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573220</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2958,6 +3063,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573223</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3060,6 +3170,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573230</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3162,6 +3277,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573246</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3264,6 +3384,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573218</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3370,6 +3495,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105074309</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3472,6 +3602,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573219</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3574,6 +3709,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121573224</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3690,8 +3830,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121608950</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>